--- a/artfynd/A 36173-2024 artfynd.xlsx
+++ b/artfynd/A 36173-2024 artfynd.xlsx
@@ -1602,7 +1602,7 @@
         <v>119557621</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malin Halvarsson</t>
+          <t>Via Malin Halvarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 36173-2024 artfynd.xlsx
+++ b/artfynd/A 36173-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1850,6 +1850,322 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120348705</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Höksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>553542</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7015655</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120348693</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Höksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>553573</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7015628</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120348704</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Höksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>553619</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7015777</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36173-2024 artfynd.xlsx
+++ b/artfynd/A 36173-2024 artfynd.xlsx
@@ -1852,7 +1852,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348705</v>
+        <v>120348704</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553542</v>
+        <v>553619</v>
       </c>
       <c r="R12" t="n">
-        <v>7015655</v>
+        <v>7015777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348693</v>
+        <v>120348705</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553573</v>
+        <v>553542</v>
       </c>
       <c r="R13" t="n">
-        <v>7015628</v>
+        <v>7015655</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,6 +2035,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348704</v>
+        <v>120348693</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,21 +2082,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2101,10 +2106,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553619</v>
+        <v>553573</v>
       </c>
       <c r="R14" t="n">
-        <v>7015777</v>
+        <v>7015628</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,11 +2142,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 36173-2024 artfynd.xlsx
+++ b/artfynd/A 36173-2024 artfynd.xlsx
@@ -1852,7 +1852,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348704</v>
+        <v>120348705</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553619</v>
+        <v>553542</v>
       </c>
       <c r="R12" t="n">
-        <v>7015777</v>
+        <v>7015655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348705</v>
+        <v>120348693</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553542</v>
+        <v>553573</v>
       </c>
       <c r="R13" t="n">
-        <v>7015655</v>
+        <v>7015628</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,11 +2035,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348693</v>
+        <v>120348704</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,21 +2077,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2106,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553573</v>
+        <v>553619</v>
       </c>
       <c r="R14" t="n">
-        <v>7015628</v>
+        <v>7015777</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,6 +2137,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 36173-2024 artfynd.xlsx
+++ b/artfynd/A 36173-2024 artfynd.xlsx
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/artfynd/A 36173-2024 artfynd.xlsx
+++ b/artfynd/A 36173-2024 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348704</v>
+        <v>120348693</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553619</v>
+        <v>553573</v>
       </c>
       <c r="R12" t="n">
-        <v>7015777</v>
+        <v>7015628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,11 +1928,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2066,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348693</v>
+        <v>120348704</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,21 +2077,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2106,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553573</v>
+        <v>553619</v>
       </c>
       <c r="R14" t="n">
-        <v>7015628</v>
+        <v>7015777</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,6 +2137,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 36173-2024 artfynd.xlsx
+++ b/artfynd/A 36173-2024 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348693</v>
+        <v>120348705</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553573</v>
+        <v>553542</v>
       </c>
       <c r="R12" t="n">
-        <v>7015628</v>
+        <v>7015655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,6 +1928,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,7 +1959,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348705</v>
+        <v>120348704</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1994,10 +1999,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553542</v>
+        <v>553619</v>
       </c>
       <c r="R13" t="n">
-        <v>7015655</v>
+        <v>7015777</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,7 +2039,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348704</v>
+        <v>120348693</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,21 +2082,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2101,10 +2106,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553619</v>
+        <v>553573</v>
       </c>
       <c r="R14" t="n">
-        <v>7015777</v>
+        <v>7015628</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,11 +2142,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 36173-2024 artfynd.xlsx
+++ b/artfynd/A 36173-2024 artfynd.xlsx
@@ -1602,7 +1602,7 @@
         <v>119557621</v>
       </c>
       <c r="B10" t="n">
-        <v>57348</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
